--- a/Laporan_Konsumsi_Pegawai_2025.xlsx
+++ b/Laporan_Konsumsi_Pegawai_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KULIAH UNAIR\PKL\Laporan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB25A1B-231C-4ECA-9E5A-BD02BB700FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD95B03-2C81-4B64-83F6-590CDB33A682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1E8E8546-A979-43BC-B6D1-D5C5BD6130E6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4198" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4197" uniqueCount="1053">
   <si>
     <t>No.</t>
   </si>
@@ -3139,9 +3139,6 @@
   </si>
   <si>
     <t>KU.02.04/1115/2025</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
   </si>
   <si>
     <t>Jumlah Pegawai</t>
@@ -3193,7 +3190,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3211,25 +3208,13 @@
       <sz val="9"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5D8DC"/>
-        <bgColor rgb="FFD6EAF8"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -3247,27 +3232,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3317,10 +3287,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3331,28 +3319,6 @@
     <xf numFmtId="3" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3667,7 +3633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81A8FFB-5C25-4A53-9E29-C504FA4EAF65}">
-  <dimension ref="A1:I700"/>
+  <dimension ref="A1:I699"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.453125" bestFit="1" customWidth="1"/>
@@ -3704,7 +3670,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>
@@ -3724,7 +3690,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>11</v>
@@ -3753,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>11</v>
@@ -3869,7 +3835,7 @@
         <v>10</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>11</v>
@@ -3985,7 +3951,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>27</v>
@@ -4043,7 +4009,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>27</v>
@@ -4101,7 +4067,7 @@
         <v>10</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>41</v>
@@ -4159,7 +4125,7 @@
         <v>10</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>41</v>
@@ -4217,7 +4183,7 @@
         <v>10</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>41</v>
@@ -4246,7 +4212,7 @@
         <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>41</v>
@@ -4478,7 +4444,7 @@
         <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>60</v>
@@ -4536,7 +4502,7 @@
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
@@ -4594,7 +4560,7 @@
         <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>70</v>
@@ -4710,7 +4676,7 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>85</v>
@@ -4739,7 +4705,7 @@
         <v>10</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>85</v>
@@ -4942,7 +4908,7 @@
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>85</v>
@@ -4971,7 +4937,7 @@
         <v>10</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>97</v>
@@ -5000,7 +4966,7 @@
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>97</v>
@@ -5029,7 +4995,7 @@
         <v>10</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>97</v>
@@ -5087,7 +5053,7 @@
         <v>10</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>104</v>
@@ -5203,7 +5169,7 @@
         <v>10</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>104</v>
@@ -5261,7 +5227,7 @@
         <v>10</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>104</v>
@@ -5348,7 +5314,7 @@
         <v>10</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>117</v>
@@ -5406,7 +5372,7 @@
         <v>10</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>117</v>
@@ -5493,7 +5459,7 @@
         <v>10</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>11</v>
@@ -5638,7 +5604,7 @@
         <v>10</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>27</v>
@@ -5667,7 +5633,7 @@
         <v>10</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>27</v>
@@ -5870,7 +5836,7 @@
         <v>10</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>41</v>
@@ -5899,7 +5865,7 @@
         <v>10</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>41</v>
@@ -5957,7 +5923,7 @@
         <v>10</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>41</v>
@@ -6015,7 +5981,7 @@
         <v>10</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>60</v>
@@ -6044,7 +6010,7 @@
         <v>10</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>60</v>
@@ -6131,7 +6097,7 @@
         <v>10</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>70</v>
@@ -6160,7 +6126,7 @@
         <v>10</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>70</v>
@@ -6218,7 +6184,7 @@
         <v>10</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>70</v>
@@ -6305,7 +6271,7 @@
         <v>10</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>85</v>
@@ -6363,7 +6329,7 @@
         <v>10</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>97</v>
@@ -6421,7 +6387,7 @@
         <v>10</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F95" s="5" t="s">
         <v>97</v>
@@ -6450,7 +6416,7 @@
         <v>10</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>97</v>
@@ -6479,7 +6445,7 @@
         <v>10</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>97</v>
@@ -6537,7 +6503,7 @@
         <v>10</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F99" s="5" t="s">
         <v>97</v>
@@ -6769,7 +6735,7 @@
         <v>10</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>117</v>
@@ -6856,7 +6822,7 @@
         <v>10</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>117</v>
@@ -6914,7 +6880,7 @@
         <v>10</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>117</v>
@@ -7030,7 +6996,7 @@
         <v>10</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>11</v>
@@ -7059,7 +7025,7 @@
         <v>10</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F117" s="5" t="s">
         <v>27</v>
@@ -7088,7 +7054,7 @@
         <v>10</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>27</v>
@@ -7146,7 +7112,7 @@
         <v>10</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>27</v>
@@ -7175,7 +7141,7 @@
         <v>10</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>27</v>
@@ -7291,7 +7257,7 @@
         <v>10</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>41</v>
@@ -7349,7 +7315,7 @@
         <v>10</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>41</v>
@@ -7436,7 +7402,7 @@
         <v>10</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>41</v>
@@ -7552,7 +7518,7 @@
         <v>10</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>41</v>
@@ -7639,7 +7605,7 @@
         <v>10</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>60</v>
@@ -7668,7 +7634,7 @@
         <v>10</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>60</v>
@@ -7726,7 +7692,7 @@
         <v>10</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>60</v>
@@ -7871,7 +7837,7 @@
         <v>10</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>70</v>
@@ -7900,7 +7866,7 @@
         <v>10</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>70</v>
@@ -7958,7 +7924,7 @@
         <v>10</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>70</v>
@@ -8132,7 +8098,7 @@
         <v>10</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>85</v>
@@ -8190,7 +8156,7 @@
         <v>10</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>85</v>
@@ -8248,7 +8214,7 @@
         <v>10</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>85</v>
@@ -8335,7 +8301,7 @@
         <v>10</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>97</v>
@@ -8393,7 +8359,7 @@
         <v>10</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>97</v>
@@ -8451,7 +8417,7 @@
         <v>10</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>97</v>
@@ -8480,7 +8446,7 @@
         <v>10</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>104</v>
@@ -8567,7 +8533,7 @@
         <v>10</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>104</v>
@@ -8799,7 +8765,7 @@
         <v>10</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>117</v>
@@ -8828,7 +8794,7 @@
         <v>10</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>11</v>
@@ -8915,7 +8881,7 @@
         <v>10</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F181" s="5" t="s">
         <v>11</v>
@@ -8944,7 +8910,7 @@
         <v>10</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>11</v>
@@ -9089,7 +9055,7 @@
         <v>10</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>27</v>
@@ -9205,7 +9171,7 @@
         <v>10</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F191" s="5" t="s">
         <v>27</v>
@@ -9263,7 +9229,7 @@
         <v>10</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F193" s="5" t="s">
         <v>27</v>
@@ -9292,7 +9258,7 @@
         <v>10</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>27</v>
@@ -9321,7 +9287,7 @@
         <v>10</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>27</v>
@@ -9350,7 +9316,7 @@
         <v>10</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>41</v>
@@ -9408,7 +9374,7 @@
         <v>10</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>41</v>
@@ -9466,7 +9432,7 @@
         <v>10</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>41</v>
@@ -9524,7 +9490,7 @@
         <v>10</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>41</v>
@@ -9611,7 +9577,7 @@
         <v>10</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F205" s="5" t="s">
         <v>60</v>
@@ -9669,7 +9635,7 @@
         <v>10</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F207" s="5" t="s">
         <v>60</v>
@@ -9814,7 +9780,7 @@
         <v>10</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>70</v>
@@ -9959,7 +9925,7 @@
         <v>10</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F217" s="5" t="s">
         <v>85</v>
@@ -9988,7 +9954,7 @@
         <v>10</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>85</v>
@@ -10017,7 +9983,7 @@
         <v>10</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F219" s="5" t="s">
         <v>85</v>
@@ -10162,7 +10128,7 @@
         <v>10</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>97</v>
@@ -10220,7 +10186,7 @@
         <v>10</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>97</v>
@@ -10249,7 +10215,7 @@
         <v>10</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F227" s="5" t="s">
         <v>97</v>
@@ -10278,7 +10244,7 @@
         <v>10</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>97</v>
@@ -10365,7 +10331,7 @@
         <v>10</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F231" s="5" t="s">
         <v>97</v>
@@ -10423,7 +10389,7 @@
         <v>10</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F233" s="5" t="s">
         <v>97</v>
@@ -10568,7 +10534,7 @@
         <v>10</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F238" s="2" t="s">
         <v>104</v>
@@ -10597,7 +10563,7 @@
         <v>10</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F239" s="5" t="s">
         <v>104</v>
@@ -10626,7 +10592,7 @@
         <v>10</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>104</v>
@@ -10684,7 +10650,7 @@
         <v>10</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>104</v>
@@ -10713,7 +10679,7 @@
         <v>10</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F243" s="5" t="s">
         <v>104</v>
@@ -10858,7 +10824,7 @@
         <v>10</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F248" s="2" t="s">
         <v>117</v>
@@ -10887,7 +10853,7 @@
         <v>10</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F249" s="5" t="s">
         <v>117</v>
@@ -11090,7 +11056,7 @@
         <v>10</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F256" s="2" t="s">
         <v>11</v>
@@ -11119,7 +11085,7 @@
         <v>10</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F257" s="5" t="s">
         <v>11</v>
@@ -11206,7 +11172,7 @@
         <v>10</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F260" s="2" t="s">
         <v>11</v>
@@ -11264,7 +11230,7 @@
         <v>10</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F262" s="2" t="s">
         <v>27</v>
@@ -11380,7 +11346,7 @@
         <v>10</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>27</v>
@@ -11409,7 +11375,7 @@
         <v>10</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F267" s="5" t="s">
         <v>27</v>
@@ -11554,7 +11520,7 @@
         <v>10</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>41</v>
@@ -11670,7 +11636,7 @@
         <v>10</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F276" s="2" t="s">
         <v>41</v>
@@ -11786,7 +11752,7 @@
         <v>10</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F280" s="2" t="s">
         <v>60</v>
@@ -11815,7 +11781,7 @@
         <v>10</v>
       </c>
       <c r="E281" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F281" s="5" t="s">
         <v>60</v>
@@ -11960,7 +11926,7 @@
         <v>10</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F286" s="2" t="s">
         <v>70</v>
@@ -12018,7 +11984,7 @@
         <v>10</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F288" s="2" t="s">
         <v>85</v>
@@ -12221,7 +12187,7 @@
         <v>10</v>
       </c>
       <c r="E295" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F295" s="5" t="s">
         <v>97</v>
@@ -12250,7 +12216,7 @@
         <v>10</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F296" s="2" t="s">
         <v>97</v>
@@ -12308,7 +12274,7 @@
         <v>10</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F298" s="2" t="s">
         <v>97</v>
@@ -12337,7 +12303,7 @@
         <v>10</v>
       </c>
       <c r="E299" s="5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F299" s="5" t="s">
         <v>97</v>
@@ -12482,7 +12448,7 @@
         <v>10</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F304" s="2" t="s">
         <v>117</v>
@@ -12569,7 +12535,7 @@
         <v>10</v>
       </c>
       <c r="E307" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F307" s="5" t="s">
         <v>117</v>
@@ -12714,7 +12680,7 @@
         <v>10</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F312" s="2" t="s">
         <v>11</v>
@@ -12743,7 +12709,7 @@
         <v>10</v>
       </c>
       <c r="E313" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F313" s="5" t="s">
         <v>27</v>
@@ -12859,7 +12825,7 @@
         <v>10</v>
       </c>
       <c r="E317" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F317" s="5" t="s">
         <v>27</v>
@@ -13004,7 +12970,7 @@
         <v>10</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F322" s="2" t="s">
         <v>41</v>
@@ -13236,7 +13202,7 @@
         <v>10</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F330" s="2" t="s">
         <v>70</v>
@@ -13265,7 +13231,7 @@
         <v>10</v>
       </c>
       <c r="E331" s="5" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F331" s="5" t="s">
         <v>70</v>
@@ -13294,7 +13260,7 @@
         <v>10</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F332" s="2" t="s">
         <v>70</v>
@@ -13410,7 +13376,7 @@
         <v>10</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F336" s="2" t="s">
         <v>85</v>
@@ -13526,7 +13492,7 @@
         <v>10</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F340" s="2" t="s">
         <v>85</v>
@@ -13555,7 +13521,7 @@
         <v>10</v>
       </c>
       <c r="E341" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F341" s="5" t="s">
         <v>85</v>
@@ -13584,7 +13550,7 @@
         <v>10</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F342" s="2" t="s">
         <v>97</v>
@@ -13642,7 +13608,7 @@
         <v>10</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F344" s="2" t="s">
         <v>97</v>
@@ -13700,7 +13666,7 @@
         <v>10</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F346" s="2" t="s">
         <v>97</v>
@@ -13816,7 +13782,7 @@
         <v>10</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F350" s="2" t="s">
         <v>104</v>
@@ -13961,7 +13927,7 @@
         <v>10</v>
       </c>
       <c r="E355" s="5" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F355" s="5" t="s">
         <v>104</v>
@@ -14222,7 +14188,7 @@
         <v>10</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F364" s="2" t="s">
         <v>11</v>
@@ -14251,7 +14217,7 @@
         <v>10</v>
       </c>
       <c r="E365" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F365" s="5" t="s">
         <v>11</v>
@@ -14367,7 +14333,7 @@
         <v>10</v>
       </c>
       <c r="E369" s="5" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F369" s="5" t="s">
         <v>11</v>
@@ -14512,7 +14478,7 @@
         <v>10</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F374" s="2" t="s">
         <v>11</v>
@@ -14599,7 +14565,7 @@
         <v>10</v>
       </c>
       <c r="E377" s="5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F377" s="5" t="s">
         <v>27</v>
@@ -14715,7 +14681,7 @@
         <v>10</v>
       </c>
       <c r="E381" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F381" s="5" t="s">
         <v>41</v>
@@ -14802,7 +14768,7 @@
         <v>10</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F384" s="2" t="s">
         <v>41</v>
@@ -14918,7 +14884,7 @@
         <v>10</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F388" s="2" t="s">
         <v>41</v>
@@ -14976,7 +14942,7 @@
         <v>10</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F390" s="2" t="s">
         <v>60</v>
@@ -15005,7 +14971,7 @@
         <v>10</v>
       </c>
       <c r="E391" s="5" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F391" s="5" t="s">
         <v>60</v>
@@ -15092,7 +15058,7 @@
         <v>10</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F394" s="2" t="s">
         <v>60</v>
@@ -15150,7 +15116,7 @@
         <v>10</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F396" s="2" t="s">
         <v>70</v>
@@ -15179,7 +15145,7 @@
         <v>10</v>
       </c>
       <c r="E397" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F397" s="5" t="s">
         <v>85</v>
@@ -15208,7 +15174,7 @@
         <v>10</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F398" s="2" t="s">
         <v>85</v>
@@ -15295,7 +15261,7 @@
         <v>10</v>
       </c>
       <c r="E401" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F401" s="5" t="s">
         <v>85</v>
@@ -15440,7 +15406,7 @@
         <v>10</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F406" s="2" t="s">
         <v>97</v>
@@ -15614,7 +15580,7 @@
         <v>10</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F412" s="2" t="s">
         <v>117</v>
@@ -15672,7 +15638,7 @@
         <v>10</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F414" s="2" t="s">
         <v>117</v>
@@ -15701,7 +15667,7 @@
         <v>10</v>
       </c>
       <c r="E415" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F415" s="5" t="s">
         <v>11</v>
@@ -15759,7 +15725,7 @@
         <v>10</v>
       </c>
       <c r="E417" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F417" s="5" t="s">
         <v>11</v>
@@ -15875,7 +15841,7 @@
         <v>10</v>
       </c>
       <c r="E421" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F421" s="5" t="s">
         <v>11</v>
@@ -15904,7 +15870,7 @@
         <v>10</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F422" s="2" t="s">
         <v>11</v>
@@ -15933,7 +15899,7 @@
         <v>10</v>
       </c>
       <c r="E423" s="5" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F423" s="5" t="s">
         <v>11</v>
@@ -15962,7 +15928,7 @@
         <v>10</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F424" s="2" t="s">
         <v>11</v>
@@ -16020,7 +15986,7 @@
         <v>10</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F426" s="2" t="s">
         <v>11</v>
@@ -16049,7 +16015,7 @@
         <v>10</v>
       </c>
       <c r="E427" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F427" s="5" t="s">
         <v>27</v>
@@ -16165,7 +16131,7 @@
         <v>10</v>
       </c>
       <c r="E431" s="5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F431" s="5" t="s">
         <v>27</v>
@@ -16223,7 +16189,7 @@
         <v>10</v>
       </c>
       <c r="E433" s="5" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F433" s="5" t="s">
         <v>27</v>
@@ -16252,7 +16218,7 @@
         <v>10</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F434" s="2" t="s">
         <v>41</v>
@@ -16281,7 +16247,7 @@
         <v>10</v>
       </c>
       <c r="E435" s="5" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F435" s="5" t="s">
         <v>41</v>
@@ -16310,7 +16276,7 @@
         <v>10</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F436" s="2" t="s">
         <v>41</v>
@@ -16513,7 +16479,7 @@
         <v>10</v>
       </c>
       <c r="E443" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F443" s="5" t="s">
         <v>60</v>
@@ -16600,7 +16566,7 @@
         <v>10</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F446" s="2" t="s">
         <v>60</v>
@@ -16658,7 +16624,7 @@
         <v>10</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F448" s="2" t="s">
         <v>60</v>
@@ -16687,7 +16653,7 @@
         <v>10</v>
       </c>
       <c r="E449" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F449" s="5" t="s">
         <v>60</v>
@@ -16745,7 +16711,7 @@
         <v>10</v>
       </c>
       <c r="E451" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F451" s="5" t="s">
         <v>60</v>
@@ -16774,7 +16740,7 @@
         <v>10</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F452" s="2" t="s">
         <v>60</v>
@@ -16832,7 +16798,7 @@
         <v>10</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F454" s="2" t="s">
         <v>70</v>
@@ -16861,7 +16827,7 @@
         <v>10</v>
       </c>
       <c r="E455" s="5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F455" s="5" t="s">
         <v>70</v>
@@ -16890,7 +16856,7 @@
         <v>10</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F456" s="2" t="s">
         <v>70</v>
@@ -16919,7 +16885,7 @@
         <v>10</v>
       </c>
       <c r="E457" s="5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F457" s="5" t="s">
         <v>70</v>
@@ -17122,7 +17088,7 @@
         <v>10</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F464" s="2" t="s">
         <v>85</v>
@@ -17151,7 +17117,7 @@
         <v>10</v>
       </c>
       <c r="E465" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F465" s="5" t="s">
         <v>85</v>
@@ -17180,7 +17146,7 @@
         <v>10</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F466" s="2" t="s">
         <v>85</v>
@@ -17238,7 +17204,7 @@
         <v>10</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F468" s="2" t="s">
         <v>85</v>
@@ -17267,7 +17233,7 @@
         <v>10</v>
       </c>
       <c r="E469" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F469" s="5" t="s">
         <v>85</v>
@@ -17325,7 +17291,7 @@
         <v>10</v>
       </c>
       <c r="E471" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F471" s="5" t="s">
         <v>97</v>
@@ -17615,7 +17581,7 @@
         <v>10</v>
       </c>
       <c r="E481" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F481" s="5" t="s">
         <v>117</v>
@@ -17673,7 +17639,7 @@
         <v>10</v>
       </c>
       <c r="E483" s="5" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F483" s="5" t="s">
         <v>117</v>
@@ -17702,7 +17668,7 @@
         <v>10</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F484" s="2" t="s">
         <v>117</v>
@@ -17789,7 +17755,7 @@
         <v>10</v>
       </c>
       <c r="E487" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F487" s="5" t="s">
         <v>117</v>
@@ -17992,7 +17958,7 @@
         <v>10</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F494" s="2" t="s">
         <v>27</v>
@@ -18021,7 +17987,7 @@
         <v>10</v>
       </c>
       <c r="E495" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F495" s="5" t="s">
         <v>27</v>
@@ -18079,7 +18045,7 @@
         <v>10</v>
       </c>
       <c r="E497" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F497" s="5" t="s">
         <v>41</v>
@@ -18108,7 +18074,7 @@
         <v>10</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F498" s="2" t="s">
         <v>41</v>
@@ -18340,7 +18306,7 @@
         <v>10</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F506" s="2" t="s">
         <v>60</v>
@@ -18485,7 +18451,7 @@
         <v>10</v>
       </c>
       <c r="E511" s="5" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F511" s="5" t="s">
         <v>70</v>
@@ -18514,7 +18480,7 @@
         <v>10</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F512" s="2" t="s">
         <v>70</v>
@@ -18630,7 +18596,7 @@
         <v>10</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F516" s="2" t="s">
         <v>70</v>
@@ -18688,7 +18654,7 @@
         <v>10</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F518" s="2" t="s">
         <v>85</v>
@@ -18804,7 +18770,7 @@
         <v>10</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F522" s="2" t="s">
         <v>97</v>
@@ -18833,7 +18799,7 @@
         <v>10</v>
       </c>
       <c r="E523" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F523" s="5" t="s">
         <v>97</v>
@@ -18891,7 +18857,7 @@
         <v>10</v>
       </c>
       <c r="E525" s="5" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F525" s="5" t="s">
         <v>104</v>
@@ -18949,7 +18915,7 @@
         <v>10</v>
       </c>
       <c r="E527" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F527" s="5" t="s">
         <v>104</v>
@@ -18978,7 +18944,7 @@
         <v>10</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F528" s="2" t="s">
         <v>104</v>
@@ -19036,7 +19002,7 @@
         <v>10</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F530" s="2" t="s">
         <v>104</v>
@@ -19065,7 +19031,7 @@
         <v>10</v>
       </c>
       <c r="E531" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F531" s="5" t="s">
         <v>104</v>
@@ -19123,7 +19089,7 @@
         <v>10</v>
       </c>
       <c r="E533" s="5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F533" s="5" t="s">
         <v>117</v>
@@ -19268,7 +19234,7 @@
         <v>10</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F538" s="2" t="s">
         <v>11</v>
@@ -19297,7 +19263,7 @@
         <v>10</v>
       </c>
       <c r="E539" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F539" s="5" t="s">
         <v>11</v>
@@ -19413,7 +19379,7 @@
         <v>10</v>
       </c>
       <c r="E543" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F543" s="5" t="s">
         <v>27</v>
@@ -19529,7 +19495,7 @@
         <v>10</v>
       </c>
       <c r="E547" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F547" s="5" t="s">
         <v>41</v>
@@ -19558,7 +19524,7 @@
         <v>10</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F548" s="2" t="s">
         <v>41</v>
@@ -19587,7 +19553,7 @@
         <v>10</v>
       </c>
       <c r="E549" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F549" s="5" t="s">
         <v>41</v>
@@ -19703,7 +19669,7 @@
         <v>10</v>
       </c>
       <c r="E553" s="5" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F553" s="5" t="s">
         <v>70</v>
@@ -19732,7 +19698,7 @@
         <v>10</v>
       </c>
       <c r="E554" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F554" s="2" t="s">
         <v>70</v>
@@ -19761,7 +19727,7 @@
         <v>10</v>
       </c>
       <c r="E555" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F555" s="5" t="s">
         <v>70</v>
@@ -19819,7 +19785,7 @@
         <v>10</v>
       </c>
       <c r="E557" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F557" s="5" t="s">
         <v>70</v>
@@ -19877,7 +19843,7 @@
         <v>10</v>
       </c>
       <c r="E559" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F559" s="5" t="s">
         <v>85</v>
@@ -19906,7 +19872,7 @@
         <v>10</v>
       </c>
       <c r="E560" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F560" s="2" t="s">
         <v>85</v>
@@ -19964,7 +19930,7 @@
         <v>10</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F562" s="2" t="s">
         <v>85</v>
@@ -20022,7 +19988,7 @@
         <v>10</v>
       </c>
       <c r="E564" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F564" s="2" t="s">
         <v>85</v>
@@ -20051,7 +20017,7 @@
         <v>10</v>
       </c>
       <c r="E565" s="5" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F565" s="5" t="s">
         <v>97</v>
@@ -20080,7 +20046,7 @@
         <v>10</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F566" s="2" t="s">
         <v>97</v>
@@ -20138,7 +20104,7 @@
         <v>10</v>
       </c>
       <c r="E568" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F568" s="2" t="s">
         <v>97</v>
@@ -20167,7 +20133,7 @@
         <v>10</v>
       </c>
       <c r="E569" s="5" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F569" s="5" t="s">
         <v>97</v>
@@ -20225,7 +20191,7 @@
         <v>10</v>
       </c>
       <c r="E571" s="5" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F571" s="5" t="s">
         <v>97</v>
@@ -20341,7 +20307,7 @@
         <v>10</v>
       </c>
       <c r="E575" s="5" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F575" s="5" t="s">
         <v>104</v>
@@ -20399,7 +20365,7 @@
         <v>10</v>
       </c>
       <c r="E577" s="5" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F577" s="5" t="s">
         <v>104</v>
@@ -20457,7 +20423,7 @@
         <v>10</v>
       </c>
       <c r="E579" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F579" s="5" t="s">
         <v>104</v>
@@ -20544,7 +20510,7 @@
         <v>10</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F582" s="2" t="s">
         <v>117</v>
@@ -20573,7 +20539,7 @@
         <v>10</v>
       </c>
       <c r="E583" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F583" s="5" t="s">
         <v>117</v>
@@ -20718,7 +20684,7 @@
         <v>10</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F588" s="2" t="s">
         <v>117</v>
@@ -20834,7 +20800,7 @@
         <v>10</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F592" s="2" t="s">
         <v>11</v>
@@ -20863,7 +20829,7 @@
         <v>10</v>
       </c>
       <c r="E593" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F593" s="5" t="s">
         <v>11</v>
@@ -20921,7 +20887,7 @@
         <v>10</v>
       </c>
       <c r="E595" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F595" s="5" t="s">
         <v>27</v>
@@ -21124,7 +21090,7 @@
         <v>10</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F602" s="2" t="s">
         <v>41</v>
@@ -21298,7 +21264,7 @@
         <v>10</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F608" s="2" t="s">
         <v>60</v>
@@ -21327,7 +21293,7 @@
         <v>10</v>
       </c>
       <c r="E609" s="5" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F609" s="5" t="s">
         <v>60</v>
@@ -21356,7 +21322,7 @@
         <v>10</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F610" s="2" t="s">
         <v>60</v>
@@ -21501,7 +21467,7 @@
         <v>10</v>
       </c>
       <c r="E615" s="5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F615" s="5" t="s">
         <v>70</v>
@@ -21530,7 +21496,7 @@
         <v>10</v>
       </c>
       <c r="E616" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F616" s="2" t="s">
         <v>70</v>
@@ -21617,7 +21583,7 @@
         <v>10</v>
       </c>
       <c r="E619" s="5" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F619" s="5" t="s">
         <v>85</v>
@@ -21704,7 +21670,7 @@
         <v>10</v>
       </c>
       <c r="E622" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F622" s="2" t="s">
         <v>97</v>
@@ -21733,7 +21699,7 @@
         <v>10</v>
       </c>
       <c r="E623" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F623" s="5" t="s">
         <v>97</v>
@@ -21791,7 +21757,7 @@
         <v>10</v>
       </c>
       <c r="E625" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F625" s="5" t="s">
         <v>97</v>
@@ -21965,7 +21931,7 @@
         <v>10</v>
       </c>
       <c r="E631" s="5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F631" s="5" t="s">
         <v>104</v>
@@ -21994,7 +21960,7 @@
         <v>10</v>
       </c>
       <c r="E632" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F632" s="2" t="s">
         <v>104</v>
@@ -22110,7 +22076,7 @@
         <v>10</v>
       </c>
       <c r="E636" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F636" s="2" t="s">
         <v>117</v>
@@ -22168,7 +22134,7 @@
         <v>10</v>
       </c>
       <c r="E638" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F638" s="2" t="s">
         <v>117</v>
@@ -22255,7 +22221,7 @@
         <v>10</v>
       </c>
       <c r="E641" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F641" s="5" t="s">
         <v>117</v>
@@ -22313,7 +22279,7 @@
         <v>10</v>
       </c>
       <c r="E643" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F643" s="5" t="s">
         <v>11</v>
@@ -22371,7 +22337,7 @@
         <v>10</v>
       </c>
       <c r="E645" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F645" s="5" t="s">
         <v>11</v>
@@ -22400,7 +22366,7 @@
         <v>10</v>
       </c>
       <c r="E646" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F646" s="2" t="s">
         <v>11</v>
@@ -22458,7 +22424,7 @@
         <v>10</v>
       </c>
       <c r="E648" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F648" s="2" t="s">
         <v>11</v>
@@ -22603,7 +22569,7 @@
         <v>10</v>
       </c>
       <c r="E653" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F653" s="5" t="s">
         <v>27</v>
@@ -22632,7 +22598,7 @@
         <v>10</v>
       </c>
       <c r="E654" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F654" s="2" t="s">
         <v>27</v>
@@ -22719,7 +22685,7 @@
         <v>10</v>
       </c>
       <c r="E657" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F657" s="5" t="s">
         <v>41</v>
@@ -22748,7 +22714,7 @@
         <v>10</v>
       </c>
       <c r="E658" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F658" s="2" t="s">
         <v>41</v>
@@ -22777,7 +22743,7 @@
         <v>10</v>
       </c>
       <c r="E659" s="5" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F659" s="5" t="s">
         <v>41</v>
@@ -22864,7 +22830,7 @@
         <v>10</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F662" s="2" t="s">
         <v>41</v>
@@ -22980,7 +22946,7 @@
         <v>10</v>
       </c>
       <c r="E666" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F666" s="2" t="s">
         <v>60</v>
@@ -23038,7 +23004,7 @@
         <v>10</v>
       </c>
       <c r="E668" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F668" s="2" t="s">
         <v>60</v>
@@ -23096,7 +23062,7 @@
         <v>10</v>
       </c>
       <c r="E670" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F670" s="2" t="s">
         <v>70</v>
@@ -23357,7 +23323,7 @@
         <v>10</v>
       </c>
       <c r="E679" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F679" s="5" t="s">
         <v>85</v>
@@ -23415,7 +23381,7 @@
         <v>10</v>
       </c>
       <c r="E681" s="5" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F681" s="5" t="s">
         <v>85</v>
@@ -23444,7 +23410,7 @@
         <v>10</v>
       </c>
       <c r="E682" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F682" s="2" t="s">
         <v>85</v>
@@ -23473,7 +23439,7 @@
         <v>10</v>
       </c>
       <c r="E683" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F683" s="5" t="s">
         <v>85</v>
@@ -23531,7 +23497,7 @@
         <v>10</v>
       </c>
       <c r="E685" s="5" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F685" s="5" t="s">
         <v>85</v>
@@ -23560,7 +23526,7 @@
         <v>10</v>
       </c>
       <c r="E686" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F686" s="2" t="s">
         <v>97</v>
@@ -23589,7 +23555,7 @@
         <v>10</v>
       </c>
       <c r="E687" s="5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F687" s="5" t="s">
         <v>97</v>
@@ -23763,7 +23729,7 @@
         <v>10</v>
       </c>
       <c r="E693" s="5" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F693" s="5" t="s">
         <v>104</v>
@@ -23792,7 +23758,7 @@
         <v>10</v>
       </c>
       <c r="E694" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F694" s="2" t="s">
         <v>104</v>
@@ -23879,7 +23845,7 @@
         <v>10</v>
       </c>
       <c r="E697" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F697" s="5" t="s">
         <v>117</v>
@@ -23908,7 +23874,7 @@
         <v>10</v>
       </c>
       <c r="E698" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F698" s="2" t="s">
         <v>117</v>
@@ -23937,7 +23903,7 @@
         <v>10</v>
       </c>
       <c r="E699" s="8" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F699" s="8" t="s">
         <v>117</v>
@@ -23952,26 +23918,7 @@
         <v>179000</v>
       </c>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A700" s="11" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B700" s="11"/>
-      <c r="C700" s="11"/>
-      <c r="D700" s="11"/>
-      <c r="E700" s="11"/>
-      <c r="F700" s="11"/>
-      <c r="G700" s="11"/>
-      <c r="H700" s="11"/>
-      <c r="I700" s="12">
-        <f>SUM(I2:I699)</f>
-        <v>491874000</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A700:H700"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>